--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/94.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/94.xlsx
@@ -426,13 +426,13 @@
         <v>-8.976843406087058</v>
       </c>
       <c r="E2">
-        <v>-12.81431101721856</v>
+        <v>-8.129649941023651</v>
       </c>
       <c r="F2">
-        <v>-2.551947463214931</v>
+        <v>-1.697809550514332</v>
       </c>
       <c r="G2">
-        <v>-7.874038143820065</v>
+        <v>-6.531949620354427</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.667453136858059</v>
       </c>
       <c r="E3">
-        <v>-12.56889489684687</v>
+        <v>-11.23221163858079</v>
       </c>
       <c r="F3">
-        <v>-2.159424741030982</v>
+        <v>-2.056773452476067</v>
       </c>
       <c r="G3">
-        <v>-7.5697507812834</v>
+        <v>-5.857314061624797</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.336700655665947</v>
       </c>
       <c r="E4">
-        <v>-13.82709517208602</v>
+        <v>-10.47022343120613</v>
       </c>
       <c r="F4">
-        <v>-2.119360751594584</v>
+        <v>-1.938745179822986</v>
       </c>
       <c r="G4">
-        <v>-7.50368338518398</v>
+        <v>-6.79447687610404</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.038475661160398</v>
       </c>
       <c r="E5">
-        <v>-13.96649065899013</v>
+        <v>-13.03916786559542</v>
       </c>
       <c r="F5">
-        <v>-2.343063853822799</v>
+        <v>-1.787665876165606</v>
       </c>
       <c r="G5">
-        <v>-6.905887472933426</v>
+        <v>-6.782579166729493</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.754582428252966</v>
       </c>
       <c r="E6">
-        <v>-13.92564835191495</v>
+        <v>-13.02789649379033</v>
       </c>
       <c r="F6">
-        <v>-2.33494171143835</v>
+        <v>-1.567488305603706</v>
       </c>
       <c r="G6">
-        <v>-7.300848112043786</v>
+        <v>-5.623234996795571</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.480991542811987</v>
       </c>
       <c r="E7">
-        <v>-15.53119616896443</v>
+        <v>-12.54851676381235</v>
       </c>
       <c r="F7">
-        <v>-1.942228464751757</v>
+        <v>-1.606573164769995</v>
       </c>
       <c r="G7">
-        <v>-7.463055299834936</v>
+        <v>-5.704159764116155</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.197942145810406</v>
       </c>
       <c r="E8">
-        <v>-16.07542364673225</v>
+        <v>-13.94428302245651</v>
       </c>
       <c r="F8">
-        <v>-2.094839419736913</v>
+        <v>-1.677265210557502</v>
       </c>
       <c r="G8">
-        <v>-6.673934639674719</v>
+        <v>-6.265068183595432</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.89027595440208</v>
       </c>
       <c r="E9">
-        <v>-15.89206573416168</v>
+        <v>-14.59198160282559</v>
       </c>
       <c r="F9">
-        <v>-2.011161058175718</v>
+        <v>-1.929873364939003</v>
       </c>
       <c r="G9">
-        <v>-6.660074759807625</v>
+        <v>-6.998158704406571</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.551922744664254</v>
       </c>
       <c r="E10">
-        <v>-17.13992750324131</v>
+        <v>-16.19476705073039</v>
       </c>
       <c r="F10">
-        <v>-2.195550671834472</v>
+        <v>-1.265714889131249</v>
       </c>
       <c r="G10">
-        <v>-6.762527621779727</v>
+        <v>-4.694806794107569</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.174811785156615</v>
       </c>
       <c r="E11">
-        <v>-18.02680196679951</v>
+        <v>-14.59503379430676</v>
       </c>
       <c r="F11">
-        <v>-1.6454260810635</v>
+        <v>-1.701789855884784</v>
       </c>
       <c r="G11">
-        <v>-6.038759051418971</v>
+        <v>-4.389078975306308</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.76569013329151</v>
       </c>
       <c r="E12">
-        <v>-18.85698899272968</v>
+        <v>-15.82743988159821</v>
       </c>
       <c r="F12">
-        <v>-1.776164823145138</v>
+        <v>-1.576261544766755</v>
       </c>
       <c r="G12">
-        <v>-5.389175619295701</v>
+        <v>-5.115390492375633</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.322506573555289</v>
       </c>
       <c r="E13">
-        <v>-18.4760809300485</v>
+        <v>-17.47087291219587</v>
       </c>
       <c r="F13">
-        <v>-2.120861753328457</v>
+        <v>-1.275961793903879</v>
       </c>
       <c r="G13">
-        <v>-4.846852038729119</v>
+        <v>-4.009336641788652</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.859506567434994</v>
       </c>
       <c r="E14">
-        <v>-20.19035287954814</v>
+        <v>-18.1496005964655</v>
       </c>
       <c r="F14">
-        <v>-1.713772190366279</v>
+        <v>-0.8382259505077303</v>
       </c>
       <c r="G14">
-        <v>-3.699346516181672</v>
+        <v>-3.558024303616388</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.387691806220115</v>
       </c>
       <c r="E15">
-        <v>-20.7882110749888</v>
+        <v>-19.16290099736984</v>
       </c>
       <c r="F15">
-        <v>-1.721732801107182</v>
+        <v>-1.077273730505403</v>
       </c>
       <c r="G15">
-        <v>-3.275819562174786</v>
+        <v>-2.938096551947379</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.925857715568028</v>
       </c>
       <c r="E16">
-        <v>-21.43055699908081</v>
+        <v>-18.83060157468699</v>
       </c>
       <c r="F16">
-        <v>-1.401132250303898</v>
+        <v>-0.8817069554806763</v>
       </c>
       <c r="G16">
-        <v>-3.003550359615182</v>
+        <v>-2.941463085267369</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.496335039121664</v>
       </c>
       <c r="E17">
-        <v>-22.2921625776762</v>
+        <v>-19.83560581120927</v>
       </c>
       <c r="F17">
-        <v>-1.119566856622735</v>
+        <v>-0.979743409234595</v>
       </c>
       <c r="G17">
-        <v>-2.78327211266498</v>
+        <v>-2.181640452411435</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.113443572351201</v>
       </c>
       <c r="E18">
-        <v>-22.98588856785924</v>
+        <v>-21.60236277445782</v>
       </c>
       <c r="F18">
-        <v>-1.15835184678921</v>
+        <v>-0.4492826038712784</v>
       </c>
       <c r="G18">
-        <v>-1.724960035767919</v>
+        <v>-1.399272546220556</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.792577008071914</v>
       </c>
       <c r="E19">
-        <v>-24.75077074286861</v>
+        <v>-23.53910959500629</v>
       </c>
       <c r="F19">
-        <v>-0.5055643703196853</v>
+        <v>-0.009982802818644594</v>
       </c>
       <c r="G19">
-        <v>-1.072938656025981</v>
+        <v>-1.215386327586155</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.531769891454879</v>
       </c>
       <c r="E20">
-        <v>-24.42651841849739</v>
+        <v>-22.75857728657022</v>
       </c>
       <c r="F20">
-        <v>-0.4064344715940712</v>
+        <v>-0.1513097370428655</v>
       </c>
       <c r="G20">
-        <v>-0.1626687334479472</v>
+        <v>-0.0938221426876782</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.331506817973329</v>
       </c>
       <c r="E21">
-        <v>-25.26443102108465</v>
+        <v>-23.591485925379</v>
       </c>
       <c r="F21">
-        <v>-0.541213161499162</v>
+        <v>0.09584278962379784</v>
       </c>
       <c r="G21">
-        <v>-0.3644343283597622</v>
+        <v>0.2225007405290302</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.178663265533092</v>
       </c>
       <c r="E22">
-        <v>-25.92724564769133</v>
+        <v>-25.3186594973265</v>
       </c>
       <c r="F22">
-        <v>-0.289886491489792</v>
+        <v>0.5689714586719579</v>
       </c>
       <c r="G22">
-        <v>-0.8002166448911744</v>
+        <v>0.7272543342399702</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.061079943759089</v>
       </c>
       <c r="E23">
-        <v>-26.17875256560333</v>
+        <v>-25.20474573366355</v>
       </c>
       <c r="F23">
-        <v>0.03463886406795638</v>
+        <v>0.4174531202910947</v>
       </c>
       <c r="G23">
-        <v>-0.5549879892029547</v>
+        <v>0.07768074578137819</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.962352907994465</v>
       </c>
       <c r="E24">
-        <v>-26.39606497628342</v>
+        <v>-25.71042684067808</v>
       </c>
       <c r="F24">
-        <v>-0.0940852884900728</v>
+        <v>0.7285531253516714</v>
       </c>
       <c r="G24">
-        <v>-0.7860975485208838</v>
+        <v>0.238775599463876</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.865961115977848</v>
       </c>
       <c r="E25">
-        <v>-27.16536214070646</v>
+        <v>-25.39203889014679</v>
       </c>
       <c r="F25">
-        <v>0.05366314984064982</v>
+        <v>0.7250342206245791</v>
       </c>
       <c r="G25">
-        <v>-0.9587980828591375</v>
+        <v>-0.3029704861082438</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.760107428295735</v>
       </c>
       <c r="E26">
-        <v>-26.96859994507318</v>
+        <v>-25.4022551275081</v>
       </c>
       <c r="F26">
-        <v>0.1847937097038116</v>
+        <v>0.68465627994252</v>
       </c>
       <c r="G26">
-        <v>-0.6663788987029838</v>
+        <v>0.1077695474814862</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.633026814603496</v>
       </c>
       <c r="E27">
-        <v>-27.87923078327561</v>
+        <v>-26.74417783020105</v>
       </c>
       <c r="F27">
-        <v>0.2720456482406835</v>
+        <v>0.555419367962158</v>
       </c>
       <c r="G27">
-        <v>-1.611252583846922</v>
+        <v>-0.2848515806569901</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.482059328092001</v>
       </c>
       <c r="E28">
-        <v>-27.48545279746463</v>
+        <v>-26.75258267795929</v>
       </c>
       <c r="F28">
-        <v>-0.05784669971980283</v>
+        <v>0.7013545100481524</v>
       </c>
       <c r="G28">
-        <v>-1.046669196221067</v>
+        <v>-1.170351561682776</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.304215661550593</v>
       </c>
       <c r="E29">
-        <v>-26.92381333713732</v>
+        <v>-25.26598428766928</v>
       </c>
       <c r="F29">
-        <v>0.03179176530453447</v>
+        <v>0.7809208558218506</v>
       </c>
       <c r="G29">
-        <v>-1.63566815347075</v>
+        <v>-1.543505202309067</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.104109509792968</v>
       </c>
       <c r="E30">
-        <v>-26.73412914637803</v>
+        <v>-25.9798936865045</v>
       </c>
       <c r="F30">
-        <v>0.1535667437204786</v>
+        <v>0.5235429619350301</v>
       </c>
       <c r="G30">
-        <v>-2.122142061874024</v>
+        <v>-1.957175366751381</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.8857165075044872</v>
       </c>
       <c r="E31">
-        <v>-26.53165654502108</v>
+        <v>-25.5256469872691</v>
       </c>
       <c r="F31">
-        <v>-0.02067536925398061</v>
+        <v>0.3451971168471022</v>
       </c>
       <c r="G31">
-        <v>-2.432637495601158</v>
+        <v>-0.4636486246526921</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.6555153303150473</v>
       </c>
       <c r="E32">
-        <v>-26.96632665112133</v>
+        <v>-25.15093387703041</v>
       </c>
       <c r="F32">
-        <v>-0.01460592129366864</v>
+        <v>0.7000266371014648</v>
       </c>
       <c r="G32">
-        <v>-2.588436457686712</v>
+        <v>-1.27728329108352</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.4206619064250451</v>
       </c>
       <c r="E33">
-        <v>-25.98057748607966</v>
+        <v>-26.08962314018437</v>
       </c>
       <c r="F33">
-        <v>-0.2733232852708158</v>
+        <v>0.6583332489837601</v>
       </c>
       <c r="G33">
-        <v>-2.183848714520941</v>
+        <v>-2.139309413073038</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.1882060305510139</v>
       </c>
       <c r="E34">
-        <v>-26.44266750229635</v>
+        <v>-23.75331547251711</v>
       </c>
       <c r="F34">
-        <v>-0.03378014156626879</v>
+        <v>0.3620560502288778</v>
       </c>
       <c r="G34">
-        <v>-2.326585133578345</v>
+        <v>-2.100190689641339</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.03203388466966779</v>
       </c>
       <c r="E35">
-        <v>-26.43930737458266</v>
+        <v>-25.03616876025402</v>
       </c>
       <c r="F35">
-        <v>-0.3376393871589751</v>
+        <v>0.8651757610953938</v>
       </c>
       <c r="G35">
-        <v>-2.580620587932115</v>
+        <v>-2.231705330965442</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.2323486867437649</v>
       </c>
       <c r="E36">
-        <v>-25.74789543461754</v>
+        <v>-23.09401947021439</v>
       </c>
       <c r="F36">
-        <v>-0.1220236358842917</v>
+        <v>0.3616741728561872</v>
       </c>
       <c r="G36">
-        <v>-2.683339228850532</v>
+        <v>-1.881674458668558</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.4021261619636503</v>
       </c>
       <c r="E37">
-        <v>-24.06232948185252</v>
+        <v>-24.30746030836173</v>
       </c>
       <c r="F37">
-        <v>-0.05577081100838727</v>
+        <v>0.8629358556382241</v>
       </c>
       <c r="G37">
-        <v>-2.874266948951501</v>
+        <v>-1.649544439445642</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.5310260924828791</v>
       </c>
       <c r="E38">
-        <v>-24.65044692970268</v>
+        <v>-23.00432398554447</v>
       </c>
       <c r="F38">
-        <v>-0.2980425969377559</v>
+        <v>0.4780738751953653</v>
       </c>
       <c r="G38">
-        <v>-3.421295801234327</v>
+        <v>-2.542105609267353</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.6069443317269549</v>
       </c>
       <c r="E39">
-        <v>-23.97391102685276</v>
+        <v>-22.06472449911497</v>
       </c>
       <c r="F39">
-        <v>0.09110369971238187</v>
+        <v>1.025065580448949</v>
       </c>
       <c r="G39">
-        <v>-2.923107931863835</v>
+        <v>-0.9365448382429834</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.6138878267822712</v>
       </c>
       <c r="E40">
-        <v>-23.96815533638901</v>
+        <v>-22.05136550079234</v>
       </c>
       <c r="F40">
-        <v>-0.06471303712160793</v>
+        <v>1.472082452226063</v>
       </c>
       <c r="G40">
-        <v>-2.789345653771512</v>
+        <v>-1.387305931193261</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.5410598276810018</v>
       </c>
       <c r="E41">
-        <v>-23.03026761313441</v>
+        <v>-22.58111997563164</v>
       </c>
       <c r="F41">
-        <v>0.2676180244727202</v>
+        <v>0.8784660877059092</v>
       </c>
       <c r="G41">
-        <v>-2.759142009316824</v>
+        <v>-1.21393602765688</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.3761169715751354</v>
       </c>
       <c r="E42">
-        <v>-22.63369555886069</v>
+        <v>-20.72587663027322</v>
       </c>
       <c r="F42">
-        <v>-0.09059786172428688</v>
+        <v>0.7398288624385783</v>
       </c>
       <c r="G42">
-        <v>-2.536143629693842</v>
+        <v>-1.494158911276578</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.1167616476535245</v>
       </c>
       <c r="E43">
-        <v>-22.08507998977944</v>
+        <v>-20.33103445307043</v>
       </c>
       <c r="F43">
-        <v>0.2939940709452592</v>
+        <v>0.8683914833530616</v>
       </c>
       <c r="G43">
-        <v>-2.752851907587368</v>
+        <v>-1.749556072577517</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.2361609711363043</v>
       </c>
       <c r="E44">
-        <v>-21.50144573119688</v>
+        <v>-20.58656265590125</v>
       </c>
       <c r="F44">
-        <v>0.159221179611988</v>
+        <v>0.9049026049988526</v>
       </c>
       <c r="G44">
-        <v>-2.4625294240077</v>
+        <v>-1.466724617818061</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.6739885981985322</v>
       </c>
       <c r="E45">
-        <v>-21.29415483349577</v>
+        <v>-20.9773110926011</v>
       </c>
       <c r="F45">
-        <v>0.04910795749265534</v>
+        <v>0.7110679462133794</v>
       </c>
       <c r="G45">
-        <v>-2.929857404611613</v>
+        <v>-0.6591142741703733</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.180864616355406</v>
       </c>
       <c r="E46">
-        <v>-21.49647346673646</v>
+        <v>-19.79195132177533</v>
       </c>
       <c r="F46">
-        <v>0.01727876840748713</v>
+        <v>0.403143901775136</v>
       </c>
       <c r="G46">
-        <v>-2.967145206413143</v>
+        <v>-1.977758469593778</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.7405727932191</v>
       </c>
       <c r="E47">
-        <v>-19.90853235662879</v>
+        <v>-19.57948890675746</v>
       </c>
       <c r="F47">
-        <v>-0.058234375664313</v>
+        <v>0.6274409434311582</v>
       </c>
       <c r="G47">
-        <v>-2.202066056618978</v>
+        <v>-1.225285773031</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.327246834978615</v>
       </c>
       <c r="E48">
-        <v>-19.63736733304949</v>
+        <v>-18.9779083056825</v>
       </c>
       <c r="F48">
-        <v>0.3974530177179034</v>
+        <v>0.872298064024664</v>
       </c>
       <c r="G48">
-        <v>-2.459517262616129</v>
+        <v>-1.529028452788797</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.921603707017034</v>
       </c>
       <c r="E49">
-        <v>-19.08074542192269</v>
+        <v>-19.57017836419769</v>
       </c>
       <c r="F49">
-        <v>-0.0004847421781454629</v>
+        <v>0.554026882358052</v>
       </c>
       <c r="G49">
-        <v>-2.924479482475683</v>
+        <v>-0.9699214239456551</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.498922810749499</v>
       </c>
       <c r="E50">
-        <v>-18.84371150693919</v>
+        <v>-17.68814456660989</v>
       </c>
       <c r="F50">
-        <v>0.2671011232133733</v>
+        <v>0.3743415671797972</v>
       </c>
       <c r="G50">
-        <v>-2.816054797265392</v>
+        <v>-2.083449897245051</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.042391358363393</v>
       </c>
       <c r="E51">
-        <v>-18.09283164630535</v>
+        <v>-16.45692041103443</v>
       </c>
       <c r="F51">
-        <v>-0.004223992634382431</v>
+        <v>0.05501421707461582</v>
       </c>
       <c r="G51">
-        <v>-2.964516947944028</v>
+        <v>-0.9876268954804188</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.537034745711792</v>
       </c>
       <c r="E52">
-        <v>-17.7982589405804</v>
+        <v>-18.01925752910273</v>
       </c>
       <c r="F52">
-        <v>0.1457038803331057</v>
+        <v>0.6372239624582203</v>
       </c>
       <c r="G52">
-        <v>-2.662175349792113</v>
+        <v>-1.725954245900431</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.972123648018952</v>
       </c>
       <c r="E53">
-        <v>-18.07437811472409</v>
+        <v>-16.25473310353997</v>
       </c>
       <c r="F53">
-        <v>-0.2214152987091904</v>
+        <v>0.646835509432903</v>
       </c>
       <c r="G53">
-        <v>-3.515361860900488</v>
+        <v>-1.405559366728452</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.344519200408482</v>
       </c>
       <c r="E54">
-        <v>-16.98526653045735</v>
+        <v>-16.09886755666996</v>
       </c>
       <c r="F54">
-        <v>-0.1903415806953754</v>
+        <v>-0.1736781420206605</v>
       </c>
       <c r="G54">
-        <v>-3.653911441248041</v>
+        <v>-2.511521343111768</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.649299233566793</v>
       </c>
       <c r="E55">
-        <v>-17.07307364146608</v>
+        <v>-15.87471262176429</v>
       </c>
       <c r="F55">
-        <v>0.03193590123262158</v>
+        <v>0.6824486808140593</v>
       </c>
       <c r="G55">
-        <v>-4.017073762225823</v>
+        <v>-2.35840642026184</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.894384428674527</v>
       </c>
       <c r="E56">
-        <v>-15.97695650790947</v>
+        <v>-15.63901460661306</v>
       </c>
       <c r="F56">
-        <v>-0.2266356700816329</v>
+        <v>0.4409174553427935</v>
       </c>
       <c r="G56">
-        <v>-3.901879916938397</v>
+        <v>-2.297326480932777</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.082513992777756</v>
       </c>
       <c r="E57">
-        <v>-16.40001107818004</v>
+        <v>-14.99625659138635</v>
       </c>
       <c r="F57">
-        <v>-0.2372048097739518</v>
+        <v>0.3057030441838302</v>
       </c>
       <c r="G57">
-        <v>-3.606212323438393</v>
+        <v>-2.706937774306058</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.227078781709508</v>
       </c>
       <c r="E58">
-        <v>-15.84551754983683</v>
+        <v>-14.85400816585741</v>
       </c>
       <c r="F58">
-        <v>-0.04385723102132478</v>
+        <v>0.4094336954645927</v>
       </c>
       <c r="G58">
-        <v>-3.878625899746612</v>
+        <v>-2.574865325316849</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.333961810259289</v>
       </c>
       <c r="E59">
-        <v>-15.3779118522788</v>
+        <v>-14.66744409368941</v>
       </c>
       <c r="F59">
-        <v>-0.2086103953967156</v>
+        <v>0.0632506741606513</v>
       </c>
       <c r="G59">
-        <v>-4.512085409126771</v>
+        <v>-2.651416224298694</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.411548323890245</v>
       </c>
       <c r="E60">
-        <v>-15.72909954004765</v>
+        <v>-14.44953845291432</v>
       </c>
       <c r="F60">
-        <v>-0.4086346154159067</v>
+        <v>0.02817511322391183</v>
       </c>
       <c r="G60">
-        <v>-4.895446930024494</v>
+        <v>-2.273367001105712</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.462198554043077</v>
       </c>
       <c r="E61">
-        <v>-15.06037525486096</v>
+        <v>-12.41089643871925</v>
       </c>
       <c r="F61">
-        <v>-0.2286925063427841</v>
+        <v>0.3047943251429591</v>
       </c>
       <c r="G61">
-        <v>-4.962206663872957</v>
+        <v>-2.975128418467272</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.48606885452589</v>
       </c>
       <c r="E62">
-        <v>-14.25142677202675</v>
+        <v>-14.35929502288946</v>
       </c>
       <c r="F62">
-        <v>-0.253862449876847</v>
+        <v>0.1825231546527381</v>
       </c>
       <c r="G62">
-        <v>-5.097783457487653</v>
+        <v>-3.040982535165327</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.486568912889394</v>
       </c>
       <c r="E63">
-        <v>-14.04341131848442</v>
+        <v>-13.42837209265866</v>
       </c>
       <c r="F63">
-        <v>-0.005113659224989101</v>
+        <v>0.09562741409906998</v>
       </c>
       <c r="G63">
-        <v>-5.105441828607397</v>
+        <v>-3.687783491406189</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.458406893373437</v>
       </c>
       <c r="E64">
-        <v>-14.57010454489453</v>
+        <v>-13.09659344448669</v>
       </c>
       <c r="F64">
-        <v>-0.5467350586062234</v>
+        <v>0.158304176897089</v>
       </c>
       <c r="G64">
-        <v>-5.496478126732661</v>
+        <v>-4.276864479194858</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.405613392650461</v>
       </c>
       <c r="E65">
-        <v>-14.27683151120979</v>
+        <v>-12.35972921090658</v>
       </c>
       <c r="F65">
-        <v>-0.5211650136166083</v>
+        <v>0.1491167540326397</v>
       </c>
       <c r="G65">
-        <v>-5.316722966041602</v>
+        <v>-4.507006078152751</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.322451751101507</v>
       </c>
       <c r="E66">
-        <v>-14.38109962523639</v>
+        <v>-12.1594212201253</v>
       </c>
       <c r="F66">
-        <v>-0.3063726595403077</v>
+        <v>0.02633448085489133</v>
       </c>
       <c r="G66">
-        <v>-6.130416694460499</v>
+        <v>-3.264049820441058</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.214905551837003</v>
       </c>
       <c r="E67">
-        <v>-13.86476301888182</v>
+        <v>-12.01950948718432</v>
       </c>
       <c r="F67">
-        <v>-0.4824462928423566</v>
+        <v>0.09829310040127878</v>
       </c>
       <c r="G67">
-        <v>-6.448665654732602</v>
+        <v>-4.363469041034842</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.081465379776862</v>
       </c>
       <c r="E68">
-        <v>-14.00280902053164</v>
+        <v>-12.07300887911094</v>
       </c>
       <c r="F68">
-        <v>-0.7513517475065349</v>
+        <v>-0.4655036943528983</v>
       </c>
       <c r="G68">
-        <v>-6.412637842009899</v>
+        <v>-5.157160442827364</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.927322257840165</v>
       </c>
       <c r="E69">
-        <v>-13.97686992141571</v>
+        <v>-11.10536455315193</v>
       </c>
       <c r="F69">
-        <v>-0.7203451272523467</v>
+        <v>-0.5537960623476864</v>
       </c>
       <c r="G69">
-        <v>-6.252638916328256</v>
+        <v>-4.410698944161489</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.758331484618179</v>
       </c>
       <c r="E70">
-        <v>-13.70780610977597</v>
+        <v>-12.22527428914484</v>
       </c>
       <c r="F70">
-        <v>-0.6824937071488261</v>
+        <v>-0.709130689353247</v>
       </c>
       <c r="G70">
-        <v>-6.45659964846334</v>
+        <v>-4.360791564242334</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.578538291058479</v>
       </c>
       <c r="E71">
-        <v>-13.73377690820996</v>
+        <v>-11.47786323960088</v>
       </c>
       <c r="F71">
-        <v>-0.9614058400388223</v>
+        <v>0.05691366352923508</v>
       </c>
       <c r="G71">
-        <v>-6.394630498091666</v>
+        <v>-4.752726917074887</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.401925511188944</v>
       </c>
       <c r="E72">
-        <v>-13.84319842565729</v>
+        <v>-12.02884720058814</v>
       </c>
       <c r="F72">
-        <v>-1.047377950938369</v>
+        <v>-0.1879616811471324</v>
       </c>
       <c r="G72">
-        <v>-6.239868402018897</v>
+        <v>-4.751279898367172</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.23311078991047</v>
       </c>
       <c r="E73">
-        <v>-13.41501309433603</v>
+        <v>-12.53494039873736</v>
       </c>
       <c r="F73">
-        <v>-1.189456214396929</v>
+        <v>-0.3990404641566828</v>
       </c>
       <c r="G73">
-        <v>-6.36358686091776</v>
+        <v>-4.510658077748412</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.088005866015004</v>
       </c>
       <c r="E74">
-        <v>-13.84348824799378</v>
+        <v>-12.32159493128799</v>
       </c>
       <c r="F74">
-        <v>-1.296247683231036</v>
+        <v>-0.5235391145930317</v>
       </c>
       <c r="G74">
-        <v>-5.523548204598081</v>
+        <v>-5.149108325120487</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.969371479638186</v>
       </c>
       <c r="E75">
-        <v>-14.40753685649317</v>
+        <v>-11.21953643983332</v>
       </c>
       <c r="F75">
-        <v>-1.449113775376254</v>
+        <v>-0.4882738575210511</v>
       </c>
       <c r="G75">
-        <v>-5.880571360038141</v>
+        <v>-4.288588283826754</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.884888473339193</v>
       </c>
       <c r="E76">
-        <v>-14.44352011095812</v>
+        <v>-12.68889492957613</v>
       </c>
       <c r="F76">
-        <v>-1.449235545384465</v>
+        <v>-1.007845773374568</v>
       </c>
       <c r="G76">
-        <v>-6.38804836764342</v>
+        <v>-5.233320876443636</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.831184797787456</v>
       </c>
       <c r="E77">
-        <v>-14.68144613532112</v>
+        <v>-12.92776740500673</v>
       </c>
       <c r="F77">
-        <v>-1.189476923581999</v>
+        <v>-0.741848716661619</v>
       </c>
       <c r="G77">
-        <v>-5.711778760577186</v>
+        <v>-4.317899436017274</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.800107503957797</v>
       </c>
       <c r="E78">
-        <v>-15.59472613081804</v>
+        <v>-13.13986754210399</v>
       </c>
       <c r="F78">
-        <v>-1.392365638080071</v>
+        <v>-0.7337969855064078</v>
       </c>
       <c r="G78">
-        <v>-5.441543915384438</v>
+        <v>-4.138072088451906</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.784613303018641</v>
       </c>
       <c r="E79">
-        <v>-15.42914247872758</v>
+        <v>-14.35610244871405</v>
       </c>
       <c r="F79">
-        <v>-1.445599840853578</v>
+        <v>-0.9220534182014291</v>
       </c>
       <c r="G79">
-        <v>-5.487881326246916</v>
+        <v>-4.219128104634868</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.768930315925927</v>
       </c>
       <c r="E80">
-        <v>-15.89994527893503</v>
+        <v>-15.03358933110558</v>
       </c>
       <c r="F80">
-        <v>-1.773140453757517</v>
+        <v>-1.351662977376114</v>
       </c>
       <c r="G80">
-        <v>-5.739993984766851</v>
+        <v>-3.209502793236849</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.746000417485694</v>
       </c>
       <c r="E81">
-        <v>-16.49835594820462</v>
+        <v>-13.30662406896244</v>
       </c>
       <c r="F81">
-        <v>-1.571138920747843</v>
+        <v>-0.9225636925215536</v>
       </c>
       <c r="G81">
-        <v>-5.275615822344879</v>
+        <v>-3.309596456907709</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.701324927672271</v>
       </c>
       <c r="E82">
-        <v>-16.94487254230893</v>
+        <v>-14.79019291014132</v>
       </c>
       <c r="F82">
-        <v>-1.506972753359591</v>
+        <v>-1.236520736754386</v>
       </c>
       <c r="G82">
-        <v>-5.333060168186077</v>
+        <v>-3.466967124120238</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.632089185407361</v>
       </c>
       <c r="E83">
-        <v>-18.22527139713368</v>
+        <v>-16.52180891509034</v>
       </c>
       <c r="F83">
-        <v>-1.594855079489993</v>
+        <v>-1.12555429621017</v>
       </c>
       <c r="G83">
-        <v>-5.284727774615456</v>
+        <v>-3.695491080849324</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.53173922232711</v>
       </c>
       <c r="E84">
-        <v>-17.79542864432561</v>
+        <v>-15.45317056181227</v>
       </c>
       <c r="F84">
-        <v>-1.908050854079653</v>
+        <v>-0.5949758626756555</v>
       </c>
       <c r="G84">
-        <v>-5.289163986163826</v>
+        <v>-3.258616117538617</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.399622903155939</v>
       </c>
       <c r="E85">
-        <v>-19.65883682831986</v>
+        <v>-18.46534844665032</v>
       </c>
       <c r="F85">
-        <v>-1.585461393142247</v>
+        <v>-1.089113585793617</v>
       </c>
       <c r="G85">
-        <v>-4.934995493480482</v>
+        <v>-3.493987983662265</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.236879103142281</v>
       </c>
       <c r="E86">
-        <v>-20.2901604466772</v>
+        <v>-17.80862914605796</v>
       </c>
       <c r="F86">
-        <v>-1.53110889437496</v>
+        <v>-1.205992084491613</v>
       </c>
       <c r="G86">
-        <v>-4.323146109290826</v>
+        <v>-3.186691740955589</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.043307345968468</v>
       </c>
       <c r="E87">
-        <v>-20.9230554455152</v>
+        <v>-21.07911118829353</v>
       </c>
       <c r="F87">
-        <v>-1.933148729649672</v>
+        <v>-1.192010899467163</v>
       </c>
       <c r="G87">
-        <v>-4.185229804704245</v>
+        <v>-3.288540858160753</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.828889824356019</v>
       </c>
       <c r="E88">
-        <v>-22.23818769597878</v>
+        <v>-20.83137648922991</v>
       </c>
       <c r="F88">
-        <v>-1.733300123519874</v>
+        <v>-1.72425600821611</v>
       </c>
       <c r="G88">
-        <v>-4.372672867509084</v>
+        <v>-2.44627753362377</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.599504294808406</v>
       </c>
       <c r="E89">
-        <v>-24.13362124815528</v>
+        <v>-22.44558727705607</v>
       </c>
       <c r="F89">
-        <v>-1.79721860905469</v>
+        <v>-1.224691650242409</v>
       </c>
       <c r="G89">
-        <v>-4.26455989834694</v>
+        <v>-2.832395280631427</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.374002728029415</v>
       </c>
       <c r="E90">
-        <v>-24.30807165235276</v>
+        <v>-23.4191503185431</v>
       </c>
       <c r="F90">
-        <v>-1.428281991930652</v>
+        <v>-1.568223067489989</v>
       </c>
       <c r="G90">
-        <v>-3.952079325576342</v>
+        <v>-2.740379984439919</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.168622536104375</v>
       </c>
       <c r="E91">
-        <v>-27.21056083977702</v>
+        <v>-25.2475760408281</v>
       </c>
       <c r="F91">
-        <v>-1.658617831953082</v>
+        <v>-1.79934917001469</v>
       </c>
       <c r="G91">
-        <v>-4.300259588913699</v>
+        <v>-2.582228386496243</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.009566773581635</v>
       </c>
       <c r="E92">
-        <v>-28.75996463607941</v>
+        <v>-26.66068182644763</v>
       </c>
       <c r="F92">
-        <v>-1.880964068375512</v>
+        <v>-1.695599466283663</v>
       </c>
       <c r="G92">
-        <v>-3.902775690424126</v>
+        <v>-2.613393428867849</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.924754275141576</v>
       </c>
       <c r="E93">
-        <v>-31.05818783734215</v>
+        <v>-29.90806865124407</v>
       </c>
       <c r="F93">
-        <v>-2.093785736400552</v>
+        <v>-1.462101747884747</v>
       </c>
       <c r="G93">
-        <v>-4.256694810268951</v>
+        <v>-3.561518804577196</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.934833185166444</v>
       </c>
       <c r="E94">
-        <v>-32.03461966711303</v>
+        <v>-30.12659469295821</v>
       </c>
       <c r="F94">
-        <v>-1.613940664450494</v>
+        <v>-1.456125905440951</v>
       </c>
       <c r="G94">
-        <v>-4.349792909575076</v>
+        <v>-2.223282435222348</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.061871925035244</v>
       </c>
       <c r="E95">
-        <v>-34.49224515344578</v>
+        <v>-34.15233563019304</v>
       </c>
       <c r="F95">
-        <v>-1.86760664400537</v>
+        <v>-1.388578342314472</v>
       </c>
       <c r="G95">
-        <v>-4.894016317424577</v>
+        <v>-2.065285054691965</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.316701552576352</v>
       </c>
       <c r="E96">
-        <v>-36.85340735070413</v>
+        <v>-34.88299585438264</v>
       </c>
       <c r="F96">
-        <v>-1.70040979579172</v>
+        <v>-1.933527293552751</v>
       </c>
       <c r="G96">
-        <v>-4.722533116284877</v>
+        <v>-3.504681484724495</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.6948024689573</v>
       </c>
       <c r="E97">
-        <v>-38.93382000914595</v>
+        <v>-38.10558701975008</v>
       </c>
       <c r="F97">
-        <v>-1.673236031510285</v>
+        <v>-1.364217713732944</v>
       </c>
       <c r="G97">
-        <v>-4.86427860643133</v>
+        <v>-3.782722356007162</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.201869349736193</v>
       </c>
       <c r="E98">
-        <v>-40.91726898213552</v>
+        <v>-40.34320112489416</v>
       </c>
       <c r="F98">
-        <v>-1.745311450860467</v>
+        <v>-1.222348198859889</v>
       </c>
       <c r="G98">
-        <v>-5.030990911423596</v>
+        <v>-3.15743636953158</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.794690068557781</v>
       </c>
       <c r="E99">
-        <v>-43.37906519302933</v>
+        <v>-43.12456495379826</v>
       </c>
       <c r="F99">
-        <v>-1.729073793030791</v>
+        <v>-1.761766140949677</v>
       </c>
       <c r="G99">
-        <v>-4.853709791788358</v>
+        <v>-2.922445125108827</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.499764170469368</v>
       </c>
       <c r="E100">
-        <v>-45.16663955129113</v>
+        <v>-45.76635894954894</v>
       </c>
       <c r="F100">
-        <v>-1.562954650808184</v>
+        <v>-1.534389229290046</v>
       </c>
       <c r="G100">
-        <v>-5.348764094569579</v>
+        <v>-3.011297323717031</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.218121975094652</v>
       </c>
       <c r="E101">
-        <v>-47.67454694876804</v>
+        <v>-47.28254186053106</v>
       </c>
       <c r="F101">
-        <v>-1.723015942214119</v>
+        <v>-1.628241599292424</v>
       </c>
       <c r="G101">
-        <v>-5.597733342835566</v>
+        <v>-3.807354486253914</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.061966835507428</v>
       </c>
       <c r="E102">
-        <v>-50.42522696991466</v>
+        <v>-49.73373917800991</v>
       </c>
       <c r="F102">
-        <v>-1.66986126271128</v>
+        <v>-1.080228517031189</v>
       </c>
       <c r="G102">
-        <v>-5.676466254154442</v>
+        <v>-3.843277299886714</v>
       </c>
     </row>
   </sheetData>
